--- a/data/describe/few_shot/few_shot_examples.xlsx
+++ b/data/describe/few_shot/few_shot_examples.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amaca253\Documents\datomatisation\datomatisation-dev\data\describe\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amaca253\Documents\datomatisation\datomatisation-dev\data\describe\few_shot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D13B2F02-16FA-4CFD-8DE4-7D1A77617354}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FB19A5C-9D9E-46A1-98E8-EC7C324B8D5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{16C02B7C-A662-4920-9F10-20A7161C31E3}"/>
+    <workbookView xWindow="29940" yWindow="1140" windowWidth="28065" windowHeight="18870" xr2:uid="{16C02B7C-A662-4920-9F10-20A7161C31E3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,24 +37,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
-  <si>
-    <t>The candidate is very outgoing and energetic. The candidate tends to be more social. In particular they said that they start conversations. The candidate is quite sensitive and nervous. The candidate tends to feel more negative emotions and anxiety. The candidate is quite friendly and compassionate. The candidate tends to be more cooperative polite kind and friendly. The candidate is very efficient and organized. The candidate tends to be more careful or diligent. In particular they said that they pay attention to details. The candidate is relatively consistent and cautious. The candidate tends to be less open to new ideas and experiences.</t>
-  </si>
-  <si>
-    <t>The candidate is extremely solitary and reserved. The candidate tends to be less social. In particular they said that they dont talk a lot. The candidate is very resilient and confident. The candidate tends to feel less negative emotions and anxiety. In particular they said that they get stressed out easily. The candidate is relatively friendly and compassionate. The candidate tends to be more cooperative polite kind and friendly. The candidate is very extravagant and careless. The candidate tends to be less careful or diligent. In particular they said that they make a mess of things. The candidate is relatively consistent and cautious. The candidate tends to be less open to new ideas and experiences.</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>User</t>
   </si>
   <si>
     <t>Assistant</t>
-  </si>
-  <si>
-    <t>The candidate appears to be an outgoing and energetic individual who enjoys social interaction and readily engages others in conversation. They demonstrate strong organizational skills, attention to detail, and a cooperative nature, though their sensitivity may at times make them prone to stress or self-doubt. They are likely to thrive in structured, collaborative environments that value precision, clear expectations, and positive interpersonal dynamics.</t>
-  </si>
-  <si>
-    <t>The candidate appears to be a reserved and independent individual who is comfortable working alone and prefers minimal social interaction. They show confidence and emotional stability, though a tendency toward carelessness or disorganization may occasionally impact their work quality. They are likely to perform best in roles that allow autonomy, clear structure, and limited social demands, where their self-assurance and steady temperament can contribute effectively.</t>
   </si>
   <si>
     <t>According to the World Value Survey, Peruvians stand out in their emphasis on survival values, viewing work as very important, possibly because it  plays central role in stability of daily life. Peruvians are skeptical toward political institutions, with many of them reporting no confidence in parliament. In other dimensions such as tradition versus secularism, neutrality, fairness, and tranquility, Peru aligns closely with the global average. Overall, Peruvian society appears deeply focused on survival and work, while remaining cautious and distrustful of formal political authority.</t>
@@ -86,24 +74,55 @@
   <si>
     <t>Giroud is a clinical forward, receiving the ball in the final third and scoring goals. His exceptional non-penalty expected goals demonstrate that it is not by chance that he has scored so many goals this season: when he gets the ball in the final third, he often finds a way to create a good chance. While he is strong in the air, he doesn’t win the ball much on the ground and he tends to score himself rather than assisting others. Giroud is one of the absolute best goal-scoring forwards in the league.</t>
   </si>
+  <si>
+    <t>Golden Retrievers are exceptionally affectionate and adaptable family companions, known for their sweet nature and readiness to embrace new surroundings. They are highly affectionate with their families and young children, adjust with ease to new situations, and are notably low droolers, making them ideal household additions. However, these dogs are quite low on playfulness and engagement, and despite their less independent nature, they are challenging in their interactions with other dogs, often leading to social friction. Ultimately, Golden Retrievers are devoted, adaptable family members, best suited for homes that can navigate their specific social challenges with other canines.</t>
+  </si>
+  <si>
+    <t>Here is the statistical description of the dog: ```Retrievers (Golden) is quite low on playful and engaged. Retrievers (Golden) is very high on amiable and adaptable. In particular, Retrievers (Golden) indicates that Affectionate with family (on a scale of '1' to '5'). Retrievers (Golden) is quite low on independent-minded. Retrievers (Golden) is quite low on aloof and tidy. ´´´
+Here is the informative descriptiom of the cluster the dog belongs to: ```Retrievers (Golden) is family adaptable. The  family adaptable dog has the following characteristics: This cluster describes dogs that are affectionate and highly adaptable companions for families, displaying average playfulness, but they are notably challenging in their interactions with other dogs. These sweet-natured pups are highly affectionate with their families, get along wonderfully with young children, and adjust easily to new situations, with the added benefit of being low droolers. A significant weakness is their poor ability to get along with other dogs, as they possess less than a modest knack for canine social graces, and despite being inclined to be more outgoing, this doesn't translate into harmonious interactions, potentially leading to social friction..´´´</t>
+  </si>
+  <si>
+    <t>Person №1 emerges as a vibrant, forward-thinking individual who blends enthusiasm with a grounded, practical outlook.
+They excel in innovation, organization, proactive behavior, and lively engagement, supported by strong imagination, eloquence, and emotional steadiness.
+At the same time, they show more average or weaker tendencies in areas involving spontaneity, sensitivity, reservation, and highly nuanced emotional expression, often favoring routine and factual approaches over improvisation.
+Overall, Person №1 can be seen as a vibrant strategist: energetic, imaginative, orderly, and pragmatic, with a balanced but less spontaneous emotional profile.</t>
+  </si>
+  <si>
+    <t>Here is the statistical description of the person: ```Person №3 is quite low on reserved and sensitive. Person №3 is average on thoughtful and creative. Person №3 is very high on lively and casual. In particular, Person №3 indicates that they leave their belongings around. Person №3 is average on empathetic and sensible. Person №3 is very high on careful and cautious. In particular, Person №3 indicates that they worry about things. Person №3 is average on organized and proactive. Person №3 is very low on verbal and realistic. In particular, Person №3 indicates that they do not have a good imagination. Person №3 is very high on factual and routine. In particular, Person №3 indicates that they follow a schedule. Person №3 is quite high on forward planner. Person №3 is quite low on attentive and reactive. Person №3 is very low on tender and kind. In particular, Person №3 indicates that they have a soft heart. Person №3 is quite high on emotionally fluid. ´´´ 
+Here is the informative description of the cluster the person belongs to: ```Person №3 is diligent planner. The diligent planner Person №3 has the following characteristics: This cluster describes individuals who are primarily driven by facts and routine, often planning ahead and maintaining a calm exterior, yet are prone to worry and experience fluctuating emotions. Their strengths lie in their diligent preparation, preference for structured and factual approaches, and a generally unbothered demeanor that helps them stay composed. However, they exhibit weaknesses in their tendency to be highly careful and cautious, which makes them prone to worrying, and their emotional fluidity leads to frequent changes in mood.´´´"</t>
+  </si>
+  <si>
+    <t>Here is the statistical description of the person: ```Person №1 is quite low on reserved and sensitive. Person №1 is relatively on carefree and practical. Person №1 is quite high on lively and casual. Person №1 is average on eloquent and insightful. Person №1 is average on composed and independent. Person №1 is quite high on organized and proactive. Person №1 is very high on inspired and innovative. In particular, Person №1 indicates that they have a vivid imagination. Person №1 is quite high on factual and routine. Person №1 is very low on impromptu approach. Person №1 is averge on unbothered and calm. Person №1 is relatively on tender and kind. Person №1 is average on emotionally steady. ´´´
+Here is the informative description of the cluster the person belongs to: ```Person №1 is vibrant strategist. The vibrant strategist people has the following characteristics: This cluster describes individuals who are often vibrant and energetic, bringing enthusiasm to their surroundings, but may also exhibit a pragmatic yet somewhat unrefined approach to daily life and emotional expression. Their strengths include a carefree attitude, strong innovative ideas, and a preference for order and planning, demonstrating firm and rational decision-making while being less reserved and more engaging, and exhibiting a tendency towards tidiness. However, they can be less composed and independent, struggle with emotional consistency and spontaneity, may lack deep interest in abstract ideas, and sometimes exhibit a casualness that could lead to messiness.´´´</t>
+  </si>
+  <si>
+    <t>Person №3 presents as a structured, fact-driven individual who pairs a lively outward demeanor with a cautious and emotionally variable inner life.
+They show strong strengths in planning ahead, adhering to routines, exercising careful judgment, and maintaining disciplined, factual habits such as following schedules.
+However, they are weaker in areas like spontaneity, verbal expressiveness, imagination, and consistent emotional regulation, and they can be prone to worry despite an otherwise calm exterior.
+In summary, Person №3 reflects the profile of a diligent planner: orderly, cautious, routine-oriented, and emotionally shifting, yet reliably grounded in practical thinking.</t>
+  </si>
+  <si>
+    <t>Argentina is characterized by a highly engaged and discerning populace, yet one deeply affected by uncertainty and a pervasive sense of national vigilance. 
+Its citizens demonstrate a strong inclination for public action, expressing political engagement and trust in diverse groups, while also embracing change with an extremely critical and dynamic approach. 
+However, this vibrancy is overshadowed by profound anxieties about the future, national security, and internal stability, coupled with an average level of institutional trust and individual flexibility that lessens collective belief and organized civic action. 
+Argentina thus represents a society actively vocal and critically minded, yet grappling with significant underlying unease and a cautious relationship with both its future and its institutions.</t>
+  </si>
+  <si>
+    <t>"You will describe a specific country based on the provided information. Please use the statistical description enclosed with ``` ´´´ to give a concise, four sentence summary of the country. The first sentence should use varied language to give an overview of the country. The second sentence should describe the country's specific strengths based on the metrics. The third sentence should describe aspects in which the country is average and/or weak based on the statistics. Finally, summarize the country with a single concluding statement. Here is the statistical description of the country: ```Argentina is quite high on uncertain adaptability. Argentina is average on critical and diligent. Argentina is quite high on public action and sentiment. Argentina is average on institutional trust. Argentina is average on conventional and patriotic. Argentina is quite high on national vigilance. Argentina is quite high on individual and flexible. Argentina is average on content and harmonious. Argentina is extremely high on dynamic and discerning. ´´´ 
+Here is the informative descriptio of the cluster the country belongs to: ```Argentina is engaged scrutiny. The engaged scrutiny Argentina has the following characteristics: This cluster represents a populace that is outwardly engaged and somewhat vigilant, yet harbors lower trust in institutions and a reduced sense of personal contentment. Their strengths include a slightly elevated inclination for public action and sentiment, showing a willingness to engage politically and a degree of trust towards other religions, along with an average level of critical thinking and discernment in political matters. However, they exhibit significant weaknesses in their relatively low institutional trust and contentment with life, coupled with a slight disinclination towards faithful engagement and a relatively high national vigilance, indicating widespread anxieties about potential threats.´´´</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -130,21 +149,12 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -462,70 +472,84 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0B2BAE4-91EA-4C9C-84FA-0836237E6794}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="77.1796875" customWidth="1"/>
-    <col min="2" max="2" width="80.26953125" customWidth="1"/>
+    <col min="1" max="1" width="126.7265625" customWidth="1"/>
+    <col min="2" max="2" width="107" customWidth="1"/>
     <col min="3" max="3" width="59.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="179" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="111" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="2" t="s">
+    </row>
+    <row r="3" spans="1:2" ht="130" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="3"/>
-    </row>
-    <row r="3" spans="1:3" ht="112.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="2"/>
-    </row>
-    <row r="4" spans="1:3" ht="179" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
+    </row>
+    <row r="4" spans="1:2" ht="159" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="130" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
+    </row>
+    <row r="5" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="214" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="4" t="s">
+    <row r="6" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="217.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="4" t="s">
+    </row>
+    <row r="7" spans="1:2" ht="159.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="2" t="s">
+    </row>
+    <row r="8" spans="1:2" ht="174" x14ac:dyDescent="0.35">
+      <c r="A8" s="1" t="s">
         <v>13</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="203" x14ac:dyDescent="0.35">
+      <c r="A9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/data/describe/few_shot/few_shot_examples.xlsx
+++ b/data/describe/few_shot/few_shot_examples.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amaca253\Documents\datomatisation\datomatisation-dev\data\describe\few_shot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FB19A5C-9D9E-46A1-98E8-EC7C324B8D5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECE76857-E38D-49D5-AB16-A042A12AAF91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29940" yWindow="1140" windowWidth="28065" windowHeight="18870" xr2:uid="{16C02B7C-A662-4920-9F10-20A7161C31E3}"/>
+    <workbookView xWindow="55260" yWindow="1620" windowWidth="22410" windowHeight="15465" xr2:uid="{16C02B7C-A662-4920-9F10-20A7161C31E3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>User</t>
   </si>
@@ -46,16 +46,6 @@
   </si>
   <si>
     <t>According to the World Value Survey, Peruvians stand out in their emphasis on survival values, viewing work as very important, possibly because it  plays central role in stability of daily life. Peruvians are skeptical toward political institutions, with many of them reporting no confidence in parliament. In other dimensions such as tradition versus secularism, neutrality, fairness, and tranquility, Peru aligns closely with the global average. Overall, Peruvian society appears deeply focused on survival and work, while remaining cautious and distrustful of formal political authority.</t>
-  </si>
-  <si>
-    <t>Here is a statistical description of the core values of Peru. 
-According to the WVS, Peru was found to have neither an above nor a below average Traditional vs Secular Values score compared to other countries in the same wave. 
-According to the WVS, Peru was found to have below average Survival vs Self-expression Values score (e.i. value survival more compared to the average) compared to other countries in the same wave. In response to the question 'How important is work to you?', on average participants indicating that work is 'very important' . 
-According to the WVS, Peru was found to be averagely neutral compared to other countries in the same wave. 
-According to the WVS, Peru was found to have an average value of fairness compared to other countries in the same wave.  According to the WVS, Peru was found to be above averagely skeptical compared to other countries in the same wave. In response to the question 'How much confidence do you have in the parliament?', on average participants indicated that they have 'none at all'. According to the WVS, Peru was found to be neither above nor below averagely tranquil compared to other countries in the same wave.</t>
-  </si>
-  <si>
-    <t>Here is a statistical description of the societal values of Brazil. According to the WVS, Brazil was found to have neither an above nor a below average Traditional vs Secular Values score compared to other countries in the same wave. According to the WVS, Brazil was found to have neither an above nor a below average Survival vs Self-expression Values score compared to other countries in the same wave. According to the WVS, Brazil was found to be averagely neutral compared to other countries in the same wave. According to the WVS, Brazil was found to have an average value of fairness compared to other countries in the same wave. According to the WVS, Brazil was found to be neither above nor below averagely skeptical compared to other countries in the same wave. According to the WVS, Brazil was found to be neither above nor below averagely tranquil compared to other countries in the same wave.</t>
   </si>
   <si>
     <t>According to the World Value Survey, Brazil does not stand out strongly in any value dimension. Brazilians show no strong leanings toward either tradition or secularism, or toward survival or self-expression priorities.  The country’s value system mirrors international norms, with neutrality and outlook aligned with the global middle ground. Although individual Brazilian citizens might have a wide range of views, on the average they do not diverge significantly from worldwide patterns.</t>
@@ -102,14 +92,12 @@
 In summary, Person №3 reflects the profile of a diligent planner: orderly, cautious, routine-oriented, and emotionally shifting, yet reliably grounded in practical thinking.</t>
   </si>
   <si>
-    <t>Argentina is characterized by a highly engaged and discerning populace, yet one deeply affected by uncertainty and a pervasive sense of national vigilance. 
-Its citizens demonstrate a strong inclination for public action, expressing political engagement and trust in diverse groups, while also embracing change with an extremely critical and dynamic approach. 
-However, this vibrancy is overshadowed by profound anxieties about the future, national security, and internal stability, coupled with an average level of institutional trust and individual flexibility that lessens collective belief and organized civic action. 
-Argentina thus represents a society actively vocal and critically minded, yet grappling with significant underlying unease and a cautious relationship with both its future and its institutions.</t>
-  </si>
-  <si>
-    <t>"You will describe a specific country based on the provided information. Please use the statistical description enclosed with ``` ´´´ to give a concise, four sentence summary of the country. The first sentence should use varied language to give an overview of the country. The second sentence should describe the country's specific strengths based on the metrics. The third sentence should describe aspects in which the country is average and/or weak based on the statistics. Finally, summarize the country with a single concluding statement. Here is the statistical description of the country: ```Argentina is quite high on uncertain adaptability. Argentina is average on critical and diligent. Argentina is quite high on public action and sentiment. Argentina is average on institutional trust. Argentina is average on conventional and patriotic. Argentina is quite high on national vigilance. Argentina is quite high on individual and flexible. Argentina is average on content and harmonious. Argentina is extremely high on dynamic and discerning. ´´´ 
-Here is the informative descriptio of the cluster the country belongs to: ```Argentina is engaged scrutiny. The engaged scrutiny Argentina has the following characteristics: This cluster represents a populace that is outwardly engaged and somewhat vigilant, yet harbors lower trust in institutions and a reduced sense of personal contentment. Their strengths include a slightly elevated inclination for public action and sentiment, showing a willingness to engage politically and a degree of trust towards other religions, along with an average level of critical thinking and discernment in political matters. However, they exhibit significant weaknesses in their relatively low institutional trust and contentment with life, coupled with a slight disinclination towards faithful engagement and a relatively high national vigilance, indicating widespread anxieties about potential threats.´´´</t>
+    <t>Here is the statistical description of the country: ```Peru is very low on engaged and faithful. In particular, Peru indicates that Most people can be trusted (on a scale of 'most people can be trusted' to  'one needs to be very careful'). Peru is quite low on skeptical and autonomous. Peru is average on individual focus. Peru is very low on systemic trust. In particular, Peru indicates that How much confidence do you have in the government? (on a scale of ' a great deal' to 'none at all'). Peru is very high on patriotic and disciplined. In particular, Peru indicates that Do you think homosexuality can always be justified, never be justified, or something in between? (on a scale of 'never justifiable' to 'always justifiable'). Peru is average on vigilant and risk-aware. Peru is average on private and worldly. Peru is quite low on content and accepting. Peru is very low on self-reliant and mindful. In particular, Peru indicates that In the future, would it be a good thing if we had greater respect for authority? (on a scale of 'good' to 'bad'). ´´´ 
+Here is the informative description of a country belongs to: ```Peru is resilient guardian. The resilient guardian Peru has the following characteristics: This cluster is characterized by individuals who exhibit a mix of patriotic and disciplined attitudes, while showing lower levels of engagement and systemic trust. Their strength lies in their vigilant and risk-aware mindset, along with a solid sense of discipline, indicating a capacity for responsibility and a proactive approach to challenges. However, this cluster has weaknesses in terms of lower engagement and a lack of contentment, which may hinder their ability to foster deeper social connections and collective wellbeing.´´´</t>
+  </si>
+  <si>
+    <t>Here is the statistical description of the country: ```Brazil is average on engaged and faithful. Brazil is quite low on skeptical and autonomous. Brazil is quite low on group membership. Brazil is very low on systemic trust. In particular, Brazil indicates that How much confidence do you have in the justice system/courts? (on a scale of ' a great deal' to 'none at all'). Brazil is very high on patriotic and disciplined. In particular, Brazil indicates that Do you think homosexuality can always be justified, never be justified, or something in between? (on a scale of 'never justifiable' to 'always justifiable'). Brazil is quite high on vigilant and risk-aware. Brazil is very high on private and worldly. Brazil is quite low on content and accepting. Brazil is average on cooperative and open. ´´´ 
+Here is the informative description of a country belongs to: ```Brazil is resilient guardian. The resilient guardian Brazil has the following characteristics: This cluster is characterized by individuals who exhibit a mix of patriotic and disciplined attitudes, while showing lower levels of engagement and systemic trust. Their strength lies in their vigilant and risk-aware mindset, along with a solid sense of discipline, indicating a capacity for responsibility and a proactive approach to challenges. However, this cluster has weaknesses in terms of lower engagement and a lack of contentment, which may hinder their ability to foster deeper social connections and collective wellbeing.´´´</t>
   </si>
 </sst>
 </file>
@@ -490,7 +478,7 @@
     </row>
     <row r="2" spans="1:2" ht="179" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>2</v>
@@ -498,59 +486,55 @@
     </row>
     <row r="3" spans="1:2" ht="130" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="159" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="174" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="203" x14ac:dyDescent="0.35">
-      <c r="A9" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>16</v>
-      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/describe/few_shot/few_shot_examples.xlsx
+++ b/data/describe/few_shot/few_shot_examples.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amaca253\Documents\datomatisation\datomatisation-dev\data\describe\few_shot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECE76857-E38D-49D5-AB16-A042A12AAF91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C8724AA-3D3F-4A88-83DB-D3A39AA788EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="55260" yWindow="1620" windowWidth="22410" windowHeight="15465" xr2:uid="{16C02B7C-A662-4920-9F10-20A7161C31E3}"/>
+    <workbookView xWindow="51150" yWindow="1305" windowWidth="27195" windowHeight="17070" xr2:uid="{16C02B7C-A662-4920-9F10-20A7161C31E3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
